--- a/Knockouts/2ndAndBelow.xlsx
+++ b/Knockouts/2ndAndBelow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\Knockouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B458FAD-EA26-4446-949E-AB58A39B5D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0318DA-1E94-4A73-9445-F6A1DF35A5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
   <sheets>
     <sheet name="Knockout Matches" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="56">
   <si>
     <t>Match</t>
   </si>
@@ -103,63 +103,9 @@
     <t>Bye</t>
   </si>
   <si>
-    <t>G1W</t>
-  </si>
-  <si>
-    <t>G2W</t>
-  </si>
-  <si>
     <t>bye</t>
   </si>
   <si>
-    <t>G4W</t>
-  </si>
-  <si>
-    <t>G3W</t>
-  </si>
-  <si>
-    <t>G6W</t>
-  </si>
-  <si>
-    <t>G8W</t>
-  </si>
-  <si>
-    <t>G5W</t>
-  </si>
-  <si>
-    <t>G7W</t>
-  </si>
-  <si>
-    <t>G9W</t>
-  </si>
-  <si>
-    <t>G1R</t>
-  </si>
-  <si>
-    <t>G2R</t>
-  </si>
-  <si>
-    <t>G3R</t>
-  </si>
-  <si>
-    <t>G4R</t>
-  </si>
-  <si>
-    <t>G5R</t>
-  </si>
-  <si>
-    <t>G7R</t>
-  </si>
-  <si>
-    <t>G8R</t>
-  </si>
-  <si>
-    <t>G6R</t>
-  </si>
-  <si>
-    <t>G9R</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -194,6 +140,96 @@
   </si>
   <si>
     <t>Saturday</t>
+  </si>
+  <si>
+    <t>Amien Phillips</t>
+  </si>
+  <si>
+    <t>NEXUS</t>
+  </si>
+  <si>
+    <t>Delton Alexander</t>
+  </si>
+  <si>
+    <t>Goodwood</t>
+  </si>
+  <si>
+    <t>Craig Fortuin</t>
+  </si>
+  <si>
+    <t>Abubakr Manuel</t>
+  </si>
+  <si>
+    <t>MP Royals</t>
+  </si>
+  <si>
+    <t>Saaliegh Jabaar</t>
+  </si>
+  <si>
+    <t>Ethan Hinrichsen</t>
+  </si>
+  <si>
+    <t>UCT</t>
+  </si>
+  <si>
+    <t>Community House</t>
+  </si>
+  <si>
+    <t>Sedick Abrahams</t>
+  </si>
+  <si>
+    <t>STEPH'S</t>
+  </si>
+  <si>
+    <t>Brendan o' Connell</t>
+  </si>
+  <si>
+    <t>Tian Louw</t>
+  </si>
+  <si>
+    <t>Maties</t>
+  </si>
+  <si>
+    <t>Janine Sait</t>
+  </si>
+  <si>
+    <t>Adam Domingo</t>
+  </si>
+  <si>
+    <t>Duinefontein TTC</t>
+  </si>
+  <si>
+    <t>DJ Swanevelder</t>
+  </si>
+  <si>
+    <t>Musfiquh Kalam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundary </t>
+  </si>
+  <si>
+    <t>Yaqeen Manuel</t>
+  </si>
+  <si>
+    <t>Graham Van As</t>
+  </si>
+  <si>
+    <t>Boundary</t>
+  </si>
+  <si>
+    <t>Valentino Esau</t>
+  </si>
+  <si>
+    <t>Mother City</t>
+  </si>
+  <si>
+    <t>Allan Clark</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Ilyaas Patel</t>
   </si>
 </sst>
 </file>
@@ -382,101 +418,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <font>
         <color theme="0" tint="-0.34998626667073579"/>
@@ -999,16 +955,16 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="M1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1023,10 +979,10 @@
       </c>
       <c r="D2" t="str" cm="1">
         <f t="array" ref="D2:F2">'Knockout Grid'!A5:C5</f>
-        <v>G1W</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+        <v>Musfiquh Kalam</v>
+      </c>
+      <c r="E2" t="str">
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1064,10 +1020,10 @@
       </c>
       <c r="G3" t="str" cm="1">
         <f t="array" ref="G3:I3">'Knockout Grid'!A10:C10</f>
-        <v>G7R</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>Abubakr Manuel</v>
+      </c>
+      <c r="H3" t="str">
+        <v>MP Royals</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1085,10 +1041,10 @@
       </c>
       <c r="D4" t="str" cm="1">
         <f t="array" ref="D4:F4">'Knockout Grid'!A13:C13</f>
-        <v>G2R</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>Ethan Hinrichsen</v>
+      </c>
+      <c r="E4" t="str">
+        <v>UCT</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1126,10 +1082,10 @@
       </c>
       <c r="G5" t="str" cm="1">
         <f t="array" ref="G5:I5">'Knockout Grid'!A18:C18</f>
-        <v>G6W</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>Adam Domingo</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Duinefontein TTC</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1147,10 +1103,10 @@
       </c>
       <c r="D6" t="str" cm="1">
         <f t="array" ref="D6:F6">'Knockout Grid'!A21:C21</f>
-        <v>G8W</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>Sedick Abrahams</v>
+      </c>
+      <c r="E6" t="str">
+        <v>STEPH'S</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1178,31 +1134,31 @@
       </c>
       <c r="D7" t="str" cm="1">
         <f t="array" ref="D7:F7">'Knockout Grid'!A25:C25</f>
-        <v>G5R</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+        <v>Delton Alexander</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" t="str" cm="1">
         <f t="array" ref="G7:I7">'Knockout Grid'!A26:C26</f>
-        <v>G3R</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v>Janine Sait</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Community House</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="16">
+        <v>25</v>
+      </c>
+      <c r="K7" s="14">
         <v>46172</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="15">
         <v>0.625</v>
       </c>
       <c r="M7">
@@ -1221,10 +1177,10 @@
       </c>
       <c r="D8" t="str" cm="1">
         <f t="array" ref="D8:F8">'Knockout Grid'!A29:C29</f>
-        <v>G9R</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+        <v>Ilyaas Patel</v>
+      </c>
+      <c r="E8" t="str">
+        <v>MP Royals</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1262,10 +1218,10 @@
       </c>
       <c r="G9" t="str" cm="1">
         <f t="array" ref="G9:I9">'Knockout Grid'!A34:C34</f>
-        <v>G4W</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>Graham Van As</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Boundary</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1283,10 +1239,10 @@
       </c>
       <c r="D10" t="str" cm="1">
         <f t="array" ref="D10:F10">'Knockout Grid'!A37:C37</f>
-        <v>G3W</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
+        <v>Tian Louw</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Maties</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1324,10 +1280,10 @@
       </c>
       <c r="G11" t="str" cm="1">
         <f t="array" ref="G11:I11">'Knockout Grid'!A42:C42</f>
-        <v>G8R</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>Brendan o' Connell</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1345,31 +1301,31 @@
       </c>
       <c r="D12" t="str" cm="1">
         <f t="array" ref="D12:F12">'Knockout Grid'!A45:C45</f>
-        <v>G1R</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
+        <v>Yaqeen Manuel</v>
+      </c>
+      <c r="E12" t="str">
+        <v>MP Royals</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12" t="str" cm="1">
         <f t="array" ref="G12:I12">'Knockout Grid'!A46:C46</f>
-        <v>G4R</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
+        <v>Valentino Esau</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Mother City</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K12" s="16">
+        <v>25</v>
+      </c>
+      <c r="K12" s="14">
         <v>46172</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="15">
         <v>0.625</v>
       </c>
       <c r="M12">
@@ -1398,10 +1354,10 @@
       </c>
       <c r="G13" t="str" cm="1">
         <f t="array" ref="G13:I13">'Knockout Grid'!A50:C50</f>
-        <v>G5W</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v>Amien Phillips</v>
+      </c>
+      <c r="H13" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1419,10 +1375,10 @@
       </c>
       <c r="D14" t="str" cm="1">
         <f t="array" ref="D14:F14">'Knockout Grid'!A53:C53</f>
-        <v>G7W</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
+        <v>Craig Fortuin</v>
+      </c>
+      <c r="E14" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1460,10 +1416,10 @@
       </c>
       <c r="G15" t="str" cm="1">
         <f t="array" ref="G15:I15">'Knockout Grid'!A58:C58</f>
-        <v>G9W</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>Allan Clark</v>
+      </c>
+      <c r="H15" t="str">
+        <v>TOP</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1481,10 +1437,10 @@
       </c>
       <c r="D16" t="str" cm="1">
         <f t="array" ref="D16:F16">'Knockout Grid'!A61:C61</f>
-        <v>G6R</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
+        <v>DJ Swanevelder</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Maties</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1522,10 +1478,10 @@
       </c>
       <c r="G17" t="str" cm="1">
         <f t="array" ref="G17:I17">'Knockout Grid'!A66:C66</f>
-        <v>G2W</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
+        <v>Saaliegh Jabaar</v>
+      </c>
+      <c r="H17" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1541,33 +1497,33 @@
       <c r="C18">
         <v>16</v>
       </c>
-      <c r="D18" cm="1">
+      <c r="D18" t="str" cm="1">
         <f t="array" ref="D18:F18">'Knockout Grid'!F7:H7</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
+        <v>Musfiquh Kalam</v>
+      </c>
+      <c r="E18" t="str">
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18" cm="1">
+      <c r="G18" t="str" cm="1">
         <f t="array" ref="G18:I18">'Knockout Grid'!F8:H8</f>
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
+        <v>Abubakr Manuel</v>
+      </c>
+      <c r="H18" t="str">
+        <v>MP Royals</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K18" s="16">
+        <v>25</v>
+      </c>
+      <c r="K18" s="14">
         <v>46172</v>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M18">
@@ -1584,33 +1540,33 @@
       <c r="C19">
         <v>16</v>
       </c>
-      <c r="D19" cm="1">
+      <c r="D19" t="str" cm="1">
         <f t="array" ref="D19:F19">'Knockout Grid'!F15:H15</f>
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
+        <v>Ethan Hinrichsen</v>
+      </c>
+      <c r="E19" t="str">
+        <v>UCT</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19" cm="1">
+      <c r="G19" t="str" cm="1">
         <f t="array" ref="G19:I19">'Knockout Grid'!F16:H16</f>
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>Adam Domingo</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Duinefontein TTC</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K19" s="16">
+        <v>25</v>
+      </c>
+      <c r="K19" s="14">
         <v>46172</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M19">
@@ -1627,12 +1583,12 @@
       <c r="C20">
         <v>16</v>
       </c>
-      <c r="D20" cm="1">
+      <c r="D20" t="str" cm="1">
         <f t="array" ref="D20:F20">'Knockout Grid'!F23:H23</f>
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
+        <v>Sedick Abrahams</v>
+      </c>
+      <c r="E20" t="str">
+        <v>STEPH'S</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1648,12 +1604,12 @@
         <v>0</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K20" s="16">
+        <v>25</v>
+      </c>
+      <c r="K20" s="14">
         <v>46172</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M20">
@@ -1670,33 +1626,33 @@
       <c r="C21">
         <v>16</v>
       </c>
-      <c r="D21" cm="1">
+      <c r="D21" t="str" cm="1">
         <f t="array" ref="D21:F21">'Knockout Grid'!F31:H31</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
+        <v>Ilyaas Patel</v>
+      </c>
+      <c r="E21" t="str">
+        <v>MP Royals</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" cm="1">
+      <c r="G21" t="str" cm="1">
         <f t="array" ref="G21:I21">'Knockout Grid'!F32:H32</f>
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
+        <v>Graham Van As</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Boundary</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="16">
+        <v>25</v>
+      </c>
+      <c r="K21" s="14">
         <v>46172</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M21">
@@ -1713,33 +1669,33 @@
       <c r="C22">
         <v>16</v>
       </c>
-      <c r="D22" cm="1">
+      <c r="D22" t="str" cm="1">
         <f t="array" ref="D22:F22">'Knockout Grid'!F39:H39</f>
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
+        <v>Tian Louw</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Maties</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22" cm="1">
+      <c r="G22" t="str" cm="1">
         <f t="array" ref="G22:I22">'Knockout Grid'!F40:H40</f>
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
+        <v>Brendan o' Connell</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K22" s="16">
+        <v>25</v>
+      </c>
+      <c r="K22" s="14">
         <v>46172</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M22">
@@ -1766,23 +1722,23 @@
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" cm="1">
+      <c r="G23" t="str" cm="1">
         <f t="array" ref="G23:I23">'Knockout Grid'!F48:H48</f>
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
+        <v>Amien Phillips</v>
+      </c>
+      <c r="H23" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K23" s="16">
+        <v>25</v>
+      </c>
+      <c r="K23" s="14">
         <v>46172</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M23">
@@ -1799,12 +1755,12 @@
       <c r="C24">
         <v>16</v>
       </c>
-      <c r="D24" cm="1">
+      <c r="D24" t="str" cm="1">
         <f t="array" ref="D24:F24">'Knockout Grid'!F55:H55</f>
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
+        <v>Craig Fortuin</v>
+      </c>
+      <c r="E24" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1820,12 +1776,12 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K24" s="16">
+        <v>25</v>
+      </c>
+      <c r="K24" s="14">
         <v>46172</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M24">
@@ -1842,33 +1798,33 @@
       <c r="C25">
         <v>16</v>
       </c>
-      <c r="D25" cm="1">
+      <c r="D25" t="str" cm="1">
         <f t="array" ref="D25:F25">'Knockout Grid'!F63:H63</f>
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
+        <v>DJ Swanevelder</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Maties</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" cm="1">
+      <c r="G25" t="str" cm="1">
         <f t="array" ref="G25:I25">'Knockout Grid'!F64:H64</f>
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
+        <v>Saaliegh Jabaar</v>
+      </c>
+      <c r="H25" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="16">
+        <v>25</v>
+      </c>
+      <c r="K25" s="14">
         <v>46172</v>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="M25">
@@ -1906,12 +1862,12 @@
         <v>0</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K26" s="16">
+        <v>25</v>
+      </c>
+      <c r="K26" s="14">
         <v>46172</v>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="M26">
@@ -1949,12 +1905,12 @@
         <v>0</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K27" s="16">
+        <v>25</v>
+      </c>
+      <c r="K27" s="14">
         <v>46172</v>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="M27">
@@ -1992,12 +1948,12 @@
         <v>0</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K28" s="16">
+        <v>25</v>
+      </c>
+      <c r="K28" s="14">
         <v>46172</v>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="M28">
@@ -2035,12 +1991,12 @@
         <v>0</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K29" s="16">
+        <v>25</v>
+      </c>
+      <c r="K29" s="14">
         <v>46172</v>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="M29">
@@ -2078,12 +2034,12 @@
         <v>0</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K30" s="16">
+        <v>25</v>
+      </c>
+      <c r="K30" s="14">
         <v>46172</v>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="15">
         <v>0.77083333333333337</v>
       </c>
       <c r="M30">
@@ -2121,12 +2077,12 @@
         <v>0</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K31" s="16">
+        <v>25</v>
+      </c>
+      <c r="K31" s="14">
         <v>46172</v>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="15">
         <v>0.77083333333333337</v>
       </c>
       <c r="M31">
@@ -2164,12 +2120,12 @@
         <v>0</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K32" s="16">
+        <v>25</v>
+      </c>
+      <c r="K32" s="14">
         <v>46172</v>
       </c>
-      <c r="L32" s="17">
+      <c r="L32" s="15">
         <v>0.77083333333333337</v>
       </c>
       <c r="M32">
@@ -2178,88 +2134,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="47" priority="47" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="31" priority="47" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",J7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="46" priority="46" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="30" priority="46" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",J12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J18">
-    <cfRule type="containsText" dxfId="45" priority="15" operator="containsText" text="Bye">
+  <conditionalFormatting sqref="J18:J32">
+    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",J18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19">
-    <cfRule type="containsText" dxfId="44" priority="14" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J19)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J20">
-    <cfRule type="containsText" dxfId="43" priority="13" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J21">
-    <cfRule type="containsText" dxfId="42" priority="12" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J21)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J22">
-    <cfRule type="containsText" dxfId="41" priority="11" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J22)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23">
-    <cfRule type="containsText" dxfId="40" priority="10" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J23)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J24">
-    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
-    <cfRule type="containsText" dxfId="38" priority="8" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J25)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J26">
-    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
-    <cfRule type="containsText" dxfId="36" priority="6" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J27)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="containsText" dxfId="35" priority="5" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J28)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J29">
-    <cfRule type="containsText" dxfId="34" priority="4" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J29)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J30">
-    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J30)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31">
-    <cfRule type="containsText" dxfId="32" priority="2" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J31)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J32">
-    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",J32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2287,93 +2173,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
+      <c r="A1" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
+      <c r="A2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
     </row>
     <row r="3" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A3" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
+      <c r="A3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -2388,18 +2274,20 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="C5" s="10"/>
       <c r="D5" s="2"/>
       <c r="F5" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="16">
+        <v>25</v>
+      </c>
+      <c r="G5" s="14">
         <v>46172</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I5">
@@ -2408,7 +2296,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="10"/>
@@ -2426,8 +2314,12 @@
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="11"/>
+      <c r="F7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="H7" s="10"/>
       <c r="I7" s="2"/>
     </row>
@@ -2442,26 +2334,30 @@
         <v>2</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="11"/>
+      <c r="F8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="H8" s="10"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="10"/>
       <c r="D9" s="5"/>
       <c r="I9" s="4"/>
       <c r="K9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="16">
+        <v>25</v>
+      </c>
+      <c r="L9" s="14">
         <v>46172</v>
       </c>
-      <c r="M9" s="17">
+      <c r="M9" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="N9">
@@ -2470,9 +2366,11 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="11"/>
+        <v>31</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="C10" s="10"/>
       <c r="I10" s="4"/>
       <c r="K10">
@@ -2511,18 +2409,20 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="11"/>
+        <v>34</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="C13" s="10"/>
       <c r="D13" s="2"/>
       <c r="F13" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="16">
+        <v>25</v>
+      </c>
+      <c r="G13" s="14">
         <v>46172</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I13" s="4">
@@ -2532,7 +2432,7 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="10"/>
@@ -2552,8 +2452,12 @@
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="11"/>
+      <c r="F15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="H15" s="10"/>
       <c r="I15" s="5"/>
       <c r="N15" s="4"/>
@@ -2569,26 +2473,30 @@
         <v>4</v>
       </c>
       <c r="D16" s="4"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="11"/>
+      <c r="F16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="H16" s="10"/>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="10"/>
       <c r="D17" s="5"/>
       <c r="N17" s="4"/>
       <c r="P17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q17" s="16">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="14">
         <v>46172</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17" s="15">
         <v>0.77083333333333337</v>
       </c>
       <c r="S17">
@@ -2597,9 +2505,11 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="11"/>
+        <v>43</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="C18" s="10"/>
       <c r="N18" s="4"/>
       <c r="P18">
@@ -2638,18 +2548,20 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="11"/>
+        <v>37</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>38</v>
+      </c>
       <c r="C21" s="10"/>
       <c r="D21" s="2"/>
       <c r="F21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="16">
+        <v>25</v>
+      </c>
+      <c r="G21" s="14">
         <v>46172</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I21">
@@ -2661,7 +2573,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="10"/>
@@ -2680,20 +2592,24 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="16">
+        <v>25</v>
+      </c>
+      <c r="B23" s="14">
         <v>46172</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="15">
         <v>0.625</v>
       </c>
       <c r="D23" s="4">
         <v>3</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="11"/>
+      <c r="F23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>38</v>
+      </c>
       <c r="H23" s="10"/>
       <c r="I23" s="2"/>
       <c r="N23" s="4"/>
@@ -2719,32 +2635,36 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="11"/>
+        <v>28</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C25" s="10"/>
       <c r="D25" s="5"/>
       <c r="I25" s="4"/>
       <c r="K25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L25" s="16">
+        <v>25</v>
+      </c>
+      <c r="L25" s="14">
         <v>46172</v>
       </c>
-      <c r="M25" s="17">
+      <c r="M25" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="N25">
         <v>6</v>
       </c>
-      <c r="O25" s="18"/>
+      <c r="O25" s="16"/>
       <c r="S25" s="4"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11"/>
+        <v>42</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="C26" s="10"/>
       <c r="I26" s="4"/>
       <c r="K26">
@@ -2786,29 +2706,31 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="11"/>
+        <v>55</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="C29" s="10"/>
       <c r="D29" s="2"/>
       <c r="F29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" s="16">
+        <v>25</v>
+      </c>
+      <c r="G29" s="14">
         <v>46172</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I29">
         <v>4</v>
       </c>
-      <c r="J29" s="18"/>
+      <c r="J29" s="16"/>
       <c r="S29" s="4"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="10"/>
@@ -2828,8 +2750,12 @@
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D31" s="4"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="11"/>
+      <c r="F31" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="H31" s="10"/>
       <c r="I31" s="5"/>
       <c r="S31" s="4"/>
@@ -2845,14 +2771,18 @@
         <v>8</v>
       </c>
       <c r="D32" s="4"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="11"/>
+      <c r="F32" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="H32" s="10"/>
       <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="10"/>
@@ -2861,18 +2791,20 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="11"/>
+        <v>49</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="C34" s="10"/>
       <c r="S34" s="4"/>
       <c r="U34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="V34" s="16">
+        <v>25</v>
+      </c>
+      <c r="V34" s="14">
         <v>46172</v>
       </c>
-      <c r="W34" s="17">
+      <c r="W34" s="15">
         <v>0.77083333333333337</v>
       </c>
       <c r="X34">
@@ -2903,18 +2835,20 @@
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="C37" s="10"/>
       <c r="D37" s="2"/>
       <c r="F37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="16">
+        <v>25</v>
+      </c>
+      <c r="G37" s="14">
         <v>46172</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I37">
@@ -2925,7 +2859,7 @@
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="10"/>
@@ -2944,8 +2878,12 @@
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D39" s="4"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="11"/>
+      <c r="F39" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="H39" s="10"/>
       <c r="I39" s="2"/>
       <c r="S39" s="4"/>
@@ -2961,27 +2899,31 @@
         <v>10</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="11"/>
+      <c r="F40" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="H40" s="10"/>
       <c r="I40" s="1"/>
       <c r="S40" s="4"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="10"/>
       <c r="D41" s="5"/>
       <c r="I41" s="4"/>
       <c r="K41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L41" s="16">
+        <v>25</v>
+      </c>
+      <c r="L41" s="14">
         <v>46172</v>
       </c>
-      <c r="M41" s="17">
+      <c r="M41" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="N41">
@@ -2991,9 +2933,11 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="11"/>
       <c r="C42" s="10"/>
       <c r="I42" s="4"/>
       <c r="K42">
@@ -3009,12 +2953,12 @@
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="16">
+        <v>25</v>
+      </c>
+      <c r="B43" s="14">
         <v>46172</v>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="15">
         <v>0.625</v>
       </c>
       <c r="D43">
@@ -3047,32 +2991,36 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="11"/>
+        <v>48</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="C45" s="10"/>
       <c r="D45" s="2"/>
       <c r="F45" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G45" s="16">
+        <v>25</v>
+      </c>
+      <c r="G45" s="14">
         <v>46172</v>
       </c>
-      <c r="H45" s="17">
+      <c r="H45" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I45">
         <v>6</v>
       </c>
-      <c r="J45" s="18"/>
+      <c r="J45" s="16"/>
       <c r="N45" s="4"/>
       <c r="S45" s="4"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" s="11"/>
+        <v>51</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>52</v>
+      </c>
       <c r="C46" s="10"/>
       <c r="D46" s="3"/>
       <c r="F46">
@@ -3109,15 +3057,19 @@
         <v>12</v>
       </c>
       <c r="D48" s="4"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="11"/>
+      <c r="F48" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="H48" s="10"/>
       <c r="N48" s="4"/>
       <c r="S48" s="4"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="10"/>
@@ -3127,18 +3079,20 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C50" s="10"/>
       <c r="N50" s="4"/>
       <c r="P50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q50" s="16">
+        <v>25</v>
+      </c>
+      <c r="Q50" s="14">
         <v>46172</v>
       </c>
-      <c r="R50" s="17">
+      <c r="R50" s="15">
         <v>0.77083333333333337</v>
       </c>
       <c r="S50">
@@ -3170,18 +3124,20 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C53" s="10"/>
       <c r="D53" s="2"/>
       <c r="F53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G53" s="16">
+        <v>25</v>
+      </c>
+      <c r="G53" s="14">
         <v>46172</v>
       </c>
-      <c r="H53" s="17">
+      <c r="H53" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I53">
@@ -3192,7 +3148,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B54" s="11"/>
       <c r="C54" s="10"/>
@@ -3211,8 +3167,12 @@
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="11"/>
+      <c r="F55" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="H55" s="10"/>
       <c r="I55" s="2"/>
       <c r="N55" s="4"/>
@@ -3236,31 +3196,33 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B57" s="11"/>
       <c r="C57" s="10"/>
       <c r="D57" s="5"/>
       <c r="I57" s="4"/>
       <c r="K57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L57" s="16">
+        <v>25</v>
+      </c>
+      <c r="L57" s="14">
         <v>46172</v>
       </c>
-      <c r="M57" s="17">
+      <c r="M57" s="15">
         <v>0.72916666666666663</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
-      <c r="O57" s="18"/>
+      <c r="O57" s="16"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B58" s="11"/>
+        <v>53</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="C58" s="10"/>
       <c r="I58" s="4"/>
       <c r="K58">
@@ -3299,18 +3261,20 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B61" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="C61" s="10"/>
       <c r="D61" s="2"/>
       <c r="F61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G61" s="16">
+        <v>25</v>
+      </c>
+      <c r="G61" s="14">
         <v>46172</v>
       </c>
-      <c r="H61" s="17">
+      <c r="H61" s="15">
         <v>0.66666666666666663</v>
       </c>
       <c r="I61" s="4">
@@ -3319,7 +3283,7 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B62" s="11"/>
       <c r="C62" s="10"/>
@@ -3338,8 +3302,12 @@
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="11"/>
+      <c r="F63" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="H63" s="10"/>
       <c r="I63" s="5"/>
     </row>
@@ -3354,8 +3322,12 @@
         <v>16</v>
       </c>
       <c r="D64" s="4"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="11"/>
+      <c r="F64" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="H64" s="10"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3368,9 +3340,11 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="11"/>
+        <v>33</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C66" s="10"/>
     </row>
   </sheetData>
@@ -3385,156 +3359,146 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A5:A66">
-    <cfRule type="containsText" dxfId="30" priority="47" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="28" priority="47" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F7:F8">
-    <cfRule type="containsText" dxfId="29" priority="45" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="26" priority="45" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="containsText" dxfId="25" priority="14" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F15:F16">
-    <cfRule type="containsText" dxfId="28" priority="43" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="24" priority="43" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="23" priority="13" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F23:F24">
-    <cfRule type="containsText" dxfId="27" priority="41" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="22" priority="41" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F23)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
+    <cfRule type="containsText" dxfId="21" priority="12" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="26" priority="39" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="20" priority="39" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F31)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F37)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F39:F40">
-    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="18" priority="37" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F45">
+    <cfRule type="containsText" dxfId="17" priority="10" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F45)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F47:F48">
-    <cfRule type="containsText" dxfId="24" priority="35" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F47)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F53">
+    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F53)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F55:F56">
-    <cfRule type="containsText" dxfId="23" priority="33" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="14" priority="33" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F55)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F61">
+    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",F61)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F63:F64">
-    <cfRule type="containsText" dxfId="22" priority="30" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="12" priority="30" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F63)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K9">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",K9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K11:K12">
-    <cfRule type="containsText" dxfId="21" priority="22" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="10" priority="22" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K11)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K25">
+    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",K25)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="8" priority="24" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K27)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K41">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",K41)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K43:K44">
-    <cfRule type="containsText" dxfId="19" priority="26" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="6" priority="26" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K43)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K57">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",K57)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K59:K60">
-    <cfRule type="containsText" dxfId="18" priority="28" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="4" priority="28" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K59)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P17">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Bye">
+      <formula>NOT(ISERROR(SEARCH("Bye",P17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P19:P20">
-    <cfRule type="containsText" dxfId="17" priority="20" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="2" priority="20" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P19)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P51:P52">
-    <cfRule type="containsText" dxfId="16" priority="17" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",P51)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U35:U36">
-    <cfRule type="containsText" dxfId="15" priority="16" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",U35)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F21)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F29)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F37)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F45">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F45)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53">
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F53)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F61">
-    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",F61)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K9">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",K9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",K25)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",K41)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K57">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",K57)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P17">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Bye">
-      <formula>NOT(ISERROR(SEARCH("Bye",P17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P50">
+  <conditionalFormatting sqref="P50:P52">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P50)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U34">
+  <conditionalFormatting sqref="U34:U36">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",U34)))</formula>
     </cfRule>

--- a/Knockouts/2ndAndBelow.xlsx
+++ b/Knockouts/2ndAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0318DA-1E94-4A73-9445-F6A1DF35A5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE700EF-57A6-4E00-AC43-C6BECBE9DAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="56">
   <si>
     <t>Match</t>
   </si>
@@ -1150,7 +1150,7 @@
         <v>Community House</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>25</v>
@@ -1307,7 +1307,7 @@
         <v>MP Royals</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="str" cm="1">
         <f t="array" ref="G12:I12">'Knockout Grid'!A46:C46</f>
@@ -1317,7 +1317,7 @@
         <v>Mother City</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>25</v>
@@ -1593,12 +1593,12 @@
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" cm="1">
+      <c r="G20" t="str" cm="1">
         <f t="array" ref="G20:I20">'Knockout Grid'!F24:H24</f>
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
+        <v>Janine Sait</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Community House</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1712,12 +1712,12 @@
       <c r="C23">
         <v>16</v>
       </c>
-      <c r="D23" cm="1">
+      <c r="D23" t="str" cm="1">
         <f t="array" ref="D23:F23">'Knockout Grid'!F47:H47</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
+        <v>Valentino Esau</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Mother City</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2626,8 +2626,12 @@
         <v>6</v>
       </c>
       <c r="D24" s="4"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="11"/>
+      <c r="F24" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="H24" s="10"/>
       <c r="I24" s="1"/>
       <c r="N24" s="4"/>
@@ -2640,7 +2644,9 @@
       <c r="B25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="10">
+        <v>0</v>
+      </c>
       <c r="D25" s="5"/>
       <c r="I25" s="4"/>
       <c r="K25" s="6" t="s">
@@ -2665,7 +2671,9 @@
       <c r="B26" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="10">
+        <v>3</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="K26">
         <v>26</v>
@@ -2996,7 +3004,9 @@
       <c r="B45" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="10">
+        <v>3</v>
+      </c>
       <c r="D45" s="2"/>
       <c r="F45" s="6" t="s">
         <v>25</v>
@@ -3021,7 +3031,9 @@
       <c r="B46" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="10"/>
+      <c r="C46" s="10">
+        <v>1</v>
+      </c>
       <c r="D46" s="3"/>
       <c r="F46">
         <v>22</v>
@@ -3039,8 +3051,12 @@
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="11"/>
+      <c r="F47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>52</v>
+      </c>
       <c r="H47" s="10"/>
       <c r="I47" s="5"/>
       <c r="N47" s="4"/>

--- a/Knockouts/2ndAndBelow.xlsx
+++ b/Knockouts/2ndAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE700EF-57A6-4E00-AC43-C6BECBE9DAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A79AB5-D15B-4C37-8839-6185515393FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="58">
   <si>
     <t>Match</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>Ilyaas Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>WO</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1511,7 @@
         <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="str" cm="1">
         <f t="array" ref="G18:I18">'Knockout Grid'!F8:H8</f>
@@ -1547,8 +1553,8 @@
       <c r="E19" t="str">
         <v>UCT</v>
       </c>
-      <c r="F19">
-        <v>0</v>
+      <c r="F19" t="str">
+        <v>WO</v>
       </c>
       <c r="G19" t="str" cm="1">
         <f t="array" ref="G19:I19">'Knockout Grid'!F16:H16</f>
@@ -1558,7 +1564,7 @@
         <v>Duinefontein TTC</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>25</v>
@@ -1591,7 +1597,7 @@
         <v>STEPH'S</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="str" cm="1">
         <f t="array" ref="G20:I20">'Knockout Grid'!F24:H24</f>
@@ -1601,7 +1607,7 @@
         <v>Community House</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>25</v>
@@ -1634,7 +1640,7 @@
         <v>MP Royals</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str" cm="1">
         <f t="array" ref="G21:I21">'Knockout Grid'!F32:H32</f>
@@ -1677,7 +1683,7 @@
         <v>Maties</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" t="str" cm="1">
         <f t="array" ref="G22:I22">'Knockout Grid'!F40:H40</f>
@@ -1687,7 +1693,7 @@
         <v>Goodwood</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>25</v>
@@ -1720,7 +1726,7 @@
         <v>Mother City</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" t="str" cm="1">
         <f t="array" ref="G23:I23">'Knockout Grid'!F48:H48</f>
@@ -1730,7 +1736,7 @@
         <v>NEXUS</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>25</v>
@@ -1763,17 +1769,17 @@
         <v>NEXUS</v>
       </c>
       <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" cm="1">
+        <v>3</v>
+      </c>
+      <c r="G24" t="str" cm="1">
         <f t="array" ref="G24:I24">'Knockout Grid'!F56:H56</f>
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
+        <v>Allan Clark</v>
+      </c>
+      <c r="H24" t="str">
+        <v>TOP</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>25</v>
@@ -1806,7 +1812,7 @@
         <v>Maties</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" t="str" cm="1">
         <f t="array" ref="G25:I25">'Knockout Grid'!F64:H64</f>
@@ -1841,22 +1847,22 @@
       <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="D26" cm="1">
+      <c r="D26" t="str" cm="1">
         <f t="array" ref="D26:F26">'Knockout Grid'!K11:M11</f>
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
+        <v>Musfiquh Kalam</v>
+      </c>
+      <c r="E26" t="str">
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="G26" cm="1">
+      <c r="G26" t="str" cm="1">
         <f t="array" ref="G26:I26">'Knockout Grid'!K12:M12</f>
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
+        <v>Adam Domingo</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Duinefontein TTC</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1884,22 +1890,22 @@
       <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="D27" cm="1">
+      <c r="D27" t="str" cm="1">
         <f t="array" ref="D27:F27">'Knockout Grid'!K27:M27</f>
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
+        <v>Sedick Abrahams</v>
+      </c>
+      <c r="E27" t="str">
+        <v>STEPH'S</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27" cm="1">
+      <c r="G27" t="str" cm="1">
         <f t="array" ref="G27:I27">'Knockout Grid'!K28:M28</f>
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
+        <v>Ilyaas Patel</v>
+      </c>
+      <c r="H27" t="str">
+        <v>MP Royals</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1927,22 +1933,22 @@
       <c r="C28" t="s">
         <v>9</v>
       </c>
-      <c r="D28" cm="1">
+      <c r="D28" t="str" cm="1">
         <f t="array" ref="D28:F28">'Knockout Grid'!K43:M43</f>
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
+        <v>Tian Louw</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Maties</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" cm="1">
+      <c r="G28" t="str" cm="1">
         <f t="array" ref="G28:I28">'Knockout Grid'!K44:M44</f>
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
+        <v>Amien Phillips</v>
+      </c>
+      <c r="H28" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1970,22 +1976,22 @@
       <c r="C29" t="s">
         <v>9</v>
       </c>
-      <c r="D29" cm="1">
+      <c r="D29" t="str" cm="1">
         <f t="array" ref="D29:F29">'Knockout Grid'!K59:M59</f>
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
+        <v>Craig Fortuin</v>
+      </c>
+      <c r="E29" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="G29" cm="1">
+      <c r="G29" t="str" cm="1">
         <f t="array" ref="G29:I29">'Knockout Grid'!K60:M60</f>
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
+        <v>DJ Swanevelder</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Maties</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2320,7 +2326,9 @@
       <c r="G7" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="10"/>
+      <c r="H7" s="10">
+        <v>3</v>
+      </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -2340,7 +2348,9 @@
       <c r="G8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
@@ -2386,8 +2396,12 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="I11" s="4"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="9"/>
+      <c r="K11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="M11" s="10"/>
       <c r="N11" s="2"/>
     </row>
@@ -2402,8 +2416,12 @@
         <v>3</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="9"/>
+      <c r="K12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="M12" s="10"/>
       <c r="N12" s="1"/>
     </row>
@@ -2458,7 +2476,9 @@
       <c r="G15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="10"/>
+      <c r="H15" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="I15" s="5"/>
       <c r="N15" s="4"/>
     </row>
@@ -2479,7 +2499,9 @@
       <c r="G16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="10"/>
+      <c r="H16" s="10">
+        <v>3</v>
+      </c>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -2610,7 +2632,9 @@
       <c r="G23" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="10"/>
+      <c r="H23" s="10">
+        <v>3</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="N23" s="4"/>
       <c r="S23" s="4"/>
@@ -2632,7 +2656,9 @@
       <c r="G24" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="10"/>
+      <c r="H24" s="10">
+        <v>1</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="N24" s="4"/>
       <c r="S24" s="4"/>
@@ -2690,8 +2716,12 @@
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="I27" s="4"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="9"/>
+      <c r="K27" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="M27" s="10"/>
       <c r="N27" s="5"/>
       <c r="S27" s="4"/>
@@ -2707,8 +2737,12 @@
         <v>7</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="9"/>
+      <c r="K28" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="M28" s="10"/>
       <c r="S28" s="4"/>
     </row>
@@ -2764,7 +2798,9 @@
       <c r="G31" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="10"/>
+      <c r="H31" s="10">
+        <v>3</v>
+      </c>
       <c r="I31" s="5"/>
       <c r="S31" s="4"/>
     </row>
@@ -2785,7 +2821,9 @@
       <c r="G32" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H32" s="10"/>
+      <c r="H32" s="10">
+        <v>0</v>
+      </c>
       <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -2892,7 +2930,9 @@
       <c r="G39" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H39" s="10"/>
+      <c r="H39" s="10">
+        <v>3</v>
+      </c>
       <c r="I39" s="2"/>
       <c r="S39" s="4"/>
     </row>
@@ -2913,7 +2953,9 @@
       <c r="G40" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H40" s="10"/>
+      <c r="H40" s="10">
+        <v>1</v>
+      </c>
       <c r="I40" s="1"/>
       <c r="S40" s="4"/>
     </row>
@@ -2974,8 +3016,12 @@
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="9"/>
+      <c r="K43" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="M43" s="10"/>
       <c r="N43" s="2"/>
       <c r="S43" s="4"/>
@@ -2990,9 +3036,16 @@
       <c r="C44">
         <v>11</v>
       </c>
+      <c r="F44" t="s">
+        <v>56</v>
+      </c>
       <c r="I44" s="4"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="9"/>
+      <c r="K44" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="M44" s="10"/>
       <c r="N44" s="1"/>
       <c r="S44" s="4"/>
@@ -3057,7 +3110,9 @@
       <c r="G47" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H47" s="10"/>
+      <c r="H47" s="10">
+        <v>2</v>
+      </c>
       <c r="I47" s="5"/>
       <c r="N47" s="4"/>
       <c r="S47" s="4"/>
@@ -3079,7 +3134,9 @@
       <c r="G48" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H48" s="10"/>
+      <c r="H48" s="10">
+        <v>3</v>
+      </c>
       <c r="N48" s="4"/>
       <c r="S48" s="4"/>
     </row>
@@ -3189,7 +3246,9 @@
       <c r="G55" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H55" s="10"/>
+      <c r="H55" s="10">
+        <v>3</v>
+      </c>
       <c r="I55" s="2"/>
       <c r="N55" s="4"/>
     </row>
@@ -3204,9 +3263,15 @@
         <v>14</v>
       </c>
       <c r="D56" s="4"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="10"/>
+      <c r="F56" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H56" s="10">
+        <v>1</v>
+      </c>
       <c r="I56" s="1"/>
       <c r="N56" s="4"/>
     </row>
@@ -3255,8 +3320,12 @@
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="I59" s="4"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="9"/>
+      <c r="K59" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="M59" s="10"/>
       <c r="N59" s="5"/>
     </row>
@@ -3271,8 +3340,12 @@
         <v>15</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="9"/>
+      <c r="K60" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="M60" s="10"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -3324,7 +3397,9 @@
       <c r="G63" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H63" s="10"/>
+      <c r="H63" s="10">
+        <v>3</v>
+      </c>
       <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -3344,7 +3419,9 @@
       <c r="G64" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H64" s="10"/>
+      <c r="H64" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">

--- a/Knockouts/2ndAndBelow.xlsx
+++ b/Knockouts/2ndAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A79AB5-D15B-4C37-8839-6185515393FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAD0D5A-3AB9-456A-A693-CBF4B4356045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="58">
   <si>
     <t>Match</t>
   </si>
@@ -1855,7 +1855,7 @@
         <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="str" cm="1">
         <f t="array" ref="G26:I26">'Knockout Grid'!K12:M12</f>
@@ -1865,7 +1865,7 @@
         <v>Duinefontein TTC</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>25</v>
@@ -1898,7 +1898,7 @@
         <v>STEPH'S</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="str" cm="1">
         <f t="array" ref="G27:I27">'Knockout Grid'!K28:M28</f>
@@ -1941,7 +1941,7 @@
         <v>Maties</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="str" cm="1">
         <f t="array" ref="G28:I28">'Knockout Grid'!K44:M44</f>
@@ -1951,7 +1951,7 @@
         <v>NEXUS</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>25</v>
@@ -1984,7 +1984,7 @@
         <v>NEXUS</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="str" cm="1">
         <f t="array" ref="G29:I29">'Knockout Grid'!K60:M60</f>
@@ -1994,7 +1994,7 @@
         <v>Maties</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>25</v>
@@ -2019,22 +2019,22 @@
       <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="D30" cm="1">
+      <c r="D30" t="str" cm="1">
         <f t="array" ref="D30:F30">'Knockout Grid'!P19:R19</f>
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
+        <v>Musfiquh Kalam</v>
+      </c>
+      <c r="E30" t="str">
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
-      <c r="G30" cm="1">
+      <c r="G30" t="str" cm="1">
         <f t="array" ref="G30:I30">'Knockout Grid'!P20:R20</f>
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
+        <v>Sedick Abrahams</v>
+      </c>
+      <c r="H30" t="str">
+        <v>STEPH'S</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2062,22 +2062,22 @@
       <c r="C31" t="s">
         <v>10</v>
       </c>
-      <c r="D31" cm="1">
+      <c r="D31" t="str" cm="1">
         <f t="array" ref="D31:F31">'Knockout Grid'!P51:R51</f>
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
+        <v>Tian Louw</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Maties</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="G31" cm="1">
+      <c r="G31" t="str" cm="1">
         <f t="array" ref="G31:I31">'Knockout Grid'!P52:R52</f>
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
+        <v>DJ Swanevelder</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Maties</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2402,7 +2402,9 @@
       <c r="L11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M11" s="10"/>
+      <c r="M11" s="10">
+        <v>3</v>
+      </c>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
@@ -2422,7 +2424,9 @@
       <c r="L12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M12" s="10"/>
+      <c r="M12" s="10">
+        <v>1</v>
+      </c>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -2547,8 +2551,12 @@
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N19" s="4"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="9"/>
+      <c r="P19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="R19" s="10"/>
       <c r="S19" s="2"/>
     </row>
@@ -2563,8 +2571,12 @@
         <v>5</v>
       </c>
       <c r="N20" s="4"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="9"/>
+      <c r="P20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="R20" s="10"/>
       <c r="S20" s="1"/>
     </row>
@@ -2722,7 +2734,9 @@
       <c r="L27" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M27" s="10"/>
+      <c r="M27" s="10">
+        <v>3</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="S27" s="4"/>
     </row>
@@ -2743,7 +2757,9 @@
       <c r="L28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="M28" s="10"/>
+      <c r="M28" s="10">
+        <v>0</v>
+      </c>
       <c r="S28" s="4"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -3022,7 +3038,9 @@
       <c r="L43" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M43" s="10"/>
+      <c r="M43" s="10">
+        <v>3</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="S43" s="4"/>
     </row>
@@ -3046,7 +3064,9 @@
       <c r="L44" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M44" s="10"/>
+      <c r="M44" s="10">
+        <v>2</v>
+      </c>
       <c r="N44" s="1"/>
       <c r="S44" s="4"/>
     </row>
@@ -3175,8 +3195,12 @@
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N51" s="4"/>
       <c r="O51" s="2"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="9"/>
+      <c r="P51" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q51" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="R51" s="10"/>
       <c r="S51" s="5"/>
     </row>
@@ -3191,8 +3215,12 @@
         <v>13</v>
       </c>
       <c r="N52" s="4"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="9"/>
+      <c r="P52" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q52" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="R52" s="10"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -3326,7 +3354,9 @@
       <c r="L59" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M59" s="10"/>
+      <c r="M59" s="10">
+        <v>1</v>
+      </c>
       <c r="N59" s="5"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -3346,7 +3376,9 @@
       <c r="L60" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M60" s="10"/>
+      <c r="M60" s="10">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
@@ -3452,147 +3484,147 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A5:A66">
-    <cfRule type="containsText" dxfId="28" priority="47" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="28" priority="48" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="27" priority="16" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F8">
-    <cfRule type="containsText" dxfId="26" priority="45" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="26" priority="46" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="containsText" dxfId="25" priority="14" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="25" priority="15" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F16">
-    <cfRule type="containsText" dxfId="24" priority="43" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="24" priority="44" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="23" priority="13" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="23" priority="14" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F24">
-    <cfRule type="containsText" dxfId="22" priority="41" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="22" priority="42" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="21" priority="12" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="21" priority="13" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="20" priority="39" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="20" priority="40" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="19" priority="12" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39:F40">
-    <cfRule type="containsText" dxfId="18" priority="37" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="18" priority="38" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45">
-    <cfRule type="containsText" dxfId="17" priority="10" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="17" priority="11" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F45)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F48">
-    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="16" priority="36" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F47)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="15" priority="10" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F53)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F56">
-    <cfRule type="containsText" dxfId="14" priority="33" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="14" priority="34" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F61">
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F61)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63:F64">
-    <cfRule type="containsText" dxfId="12" priority="30" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="12" priority="31" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K12">
-    <cfRule type="containsText" dxfId="10" priority="22" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="10" priority="23" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K25)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="containsText" dxfId="8" priority="24" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="8" priority="25" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43:K44">
-    <cfRule type="containsText" dxfId="6" priority="26" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="6" priority="27" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K43)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K57">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K57)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K59:K60">
-    <cfRule type="containsText" dxfId="4" priority="28" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="4" priority="29" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P17">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P20">
-    <cfRule type="containsText" dxfId="2" priority="20" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="2" priority="21" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P50:P52">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P50)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:U36">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",U34)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Knockouts/2ndAndBelow.xlsx
+++ b/Knockouts/2ndAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAD0D5A-3AB9-456A-A693-CBF4B4356045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66D3A68-B3FB-4B7F-9CDB-324FCE7AF127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="58">
   <si>
     <t>Match</t>
   </si>
@@ -2027,7 +2027,7 @@
         <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G30" t="str" cm="1">
         <f t="array" ref="G30:I30">'Knockout Grid'!P20:R20</f>
@@ -2070,7 +2070,7 @@
         <v>Maties</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" t="str" cm="1">
         <f t="array" ref="G31:I31">'Knockout Grid'!P52:R52</f>
@@ -2080,7 +2080,7 @@
         <v>Maties</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>25</v>
@@ -2105,22 +2105,22 @@
       <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="D32" cm="1">
+      <c r="D32" t="str" cm="1">
         <f t="array" ref="D32:F32">'Knockout Grid'!U35:W35</f>
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
+        <v>Musfiquh Kalam</v>
+      </c>
+      <c r="E32" t="str">
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
-      <c r="G32" cm="1">
+      <c r="G32" t="str" cm="1">
         <f t="array" ref="G32:I32">'Knockout Grid'!U36:W36</f>
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
+        <v>Tian Louw</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Maties</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2557,7 +2557,9 @@
       <c r="Q19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="10">
+        <v>3</v>
+      </c>
       <c r="S19" s="2"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -2577,7 +2579,9 @@
       <c r="Q20" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="R20" s="10"/>
+      <c r="R20" s="10">
+        <v>0</v>
+      </c>
       <c r="S20" s="1"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2876,8 +2880,12 @@
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="S35" s="4"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="9"/>
+      <c r="U35" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V35" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="W35" s="10"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -2891,8 +2899,12 @@
         <v>9</v>
       </c>
       <c r="S36" s="4"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="9"/>
+      <c r="U36" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="V36" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="W36" s="10"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -3201,7 +3213,9 @@
       <c r="Q51" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="R51" s="10"/>
+      <c r="R51" s="10">
+        <v>3</v>
+      </c>
       <c r="S51" s="5"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -3221,7 +3235,9 @@
       <c r="Q52" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="R52" s="10"/>
+      <c r="R52" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">

--- a/Knockouts/2ndAndBelow.xlsx
+++ b/Knockouts/2ndAndBelow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66D3A68-B3FB-4B7F-9CDB-324FCE7AF127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C3A23A-9CC1-4F0C-8B0D-9011CD3F43D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -2113,7 +2113,7 @@
         <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="str" cm="1">
         <f t="array" ref="G32:I32">'Knockout Grid'!U36:W36</f>
@@ -2123,7 +2123,7 @@
         <v>Maties</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>25</v>
@@ -2886,7 +2886,9 @@
       <c r="V35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="W35" s="10"/>
+      <c r="W35" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
@@ -2905,7 +2907,9 @@
       <c r="V36" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="W36" s="10"/>
+      <c r="W36" s="10">
+        <v>3</v>
+      </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
